--- a/docs/restated-2025/YBI-2025-AM-restated-invoices.xlsx
+++ b/docs/restated-2025/YBI-2025-AM-restated-invoices.xlsx
@@ -457,7 +457,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Fringe 21.90% · indirect combined 43.99% on MTDC · administrative labour POOL. Read from the rate on the record, not recomputed here.</t>
+          <t>Fringe 21.90% · indirect combined 24.71% on MTDC · administrative labour POOL. Read from the rate on the record, not recomputed here.</t>
         </is>
       </c>
     </row>
@@ -495,9 +495,9 @@
       <c r="A10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>No 200.465 facilities carve-out has been evaluated — no building on the record carries square footage — so every dollar of tenant and vacant occupancy cost is in the federal pool and the indirect rate reads high. At a provisional 20% tenant share the combined rate is 37.67% rather than 43.99%.</t>
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>The 200.465 facilities carve-out IS in this rate — carve-outs are recorded against the estate on the record. That estate is derived from documents rather than measured from floor plans, and the derivation takes the low side at every choice, so the carve-out is if anything too small and the rate too high. A measured floor plan arrived on 15 September 2026 and has not been accepted into the record; accepting it will move this rate, and the direction the measurement points is DOWN.</t>
         </is>
       </c>
     </row>
@@ -507,7 +507,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>0 of 43 people have certified their 2025 effort under 2 CFR 200.430(i). Every restated labour line is the management reconstruction at 100%.</t>
+          <t>No one of the 43 people has certified their 2025 effort under 2 CFR 200.430(i). Every restated labour line is the management reconstruction at 100%.</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X37"/>
+  <dimension ref="A1:X44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -722,16 +722,16 @@
         <v>17486.88</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>7692.48</v>
+        <v>4321.01</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>25179.36</v>
+        <v>21807.89</v>
       </c>
       <c r="L2" s="4" t="n">
         <v>25373.65</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>-194.29</v>
+        <v>-3565.76</v>
       </c>
     </row>
     <row r="3">
@@ -773,16 +773,16 @@
         <v>28659.7</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>12607.4</v>
+        <v>7081.81</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>41267.1</v>
+        <v>35741.51</v>
       </c>
       <c r="L3" s="4" t="n">
         <v>27798.15</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>13468.95</v>
+        <v>7943.36</v>
       </c>
     </row>
     <row r="4">
@@ -824,16 +824,16 @@
         <v>16621.06</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>7311.61</v>
+        <v>4107.06</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>23932.67</v>
+        <v>20728.12</v>
       </c>
       <c r="L4" s="4" t="n">
         <v>26032.42</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>-2099.75</v>
+        <v>-5304.3</v>
       </c>
     </row>
     <row r="5">
@@ -875,16 +875,16 @@
         <v>19336.76</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>8506.24</v>
+        <v>4778.11</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>27843</v>
+        <v>24114.87</v>
       </c>
       <c r="L5" s="4" t="n">
         <v>33785.53</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>-5942.53</v>
+        <v>-9670.66</v>
       </c>
     </row>
     <row r="6">
@@ -926,16 +926,16 @@
         <v>27752.41</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>12208.29</v>
+        <v>6857.62</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>39960.7</v>
+        <v>34610.03</v>
       </c>
       <c r="L6" s="4" t="n">
         <v>150719.52</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-110758.82</v>
+        <v>-116109.49</v>
       </c>
     </row>
     <row r="7">
@@ -977,16 +977,16 @@
         <v>17056.61</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>7503.2</v>
+        <v>4214.69</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>24559.81</v>
+        <v>21271.3</v>
       </c>
       <c r="L7" s="4" t="n">
         <v>29086.96</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-4527.15</v>
+        <v>-7815.66</v>
       </c>
     </row>
     <row r="8">
@@ -1028,16 +1028,16 @@
         <v>16783.79</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>7383.19</v>
+        <v>4147.28</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>24166.98</v>
+        <v>20931.07</v>
       </c>
       <c r="L8" s="4" t="n">
         <v>29073.65</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-4906.67</v>
+        <v>-8142.58</v>
       </c>
     </row>
     <row r="9">
@@ -1079,16 +1079,16 @@
         <v>13664.93</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>6011.2</v>
+        <v>3376.6</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>19676.13</v>
+        <v>17041.53</v>
       </c>
       <c r="L9" s="4" t="n">
         <v>25940.16</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-6264.03</v>
+        <v>-8898.629999999999</v>
       </c>
     </row>
     <row r="10">
@@ -1130,16 +1130,16 @@
         <v>39984.38</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>17589.13</v>
+        <v>9880.139999999999</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>57573.51</v>
+        <v>49864.52</v>
       </c>
       <c r="L10" s="4" t="n">
         <v>132599.96</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-75026.45</v>
+        <v>-82735.44</v>
       </c>
     </row>
     <row r="11">
@@ -1181,16 +1181,16 @@
         <v>125701.62</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>55296.14</v>
+        <v>31060.87</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>180997.76</v>
+        <v>156762.49</v>
       </c>
       <c r="L11" s="4" t="n">
         <v>62615.64</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>118382.12</v>
+        <v>94146.85000000001</v>
       </c>
     </row>
     <row r="12">
@@ -1232,16 +1232,16 @@
         <v>15039.24</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>6615.76</v>
+        <v>3716.2</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>21655</v>
+        <v>18755.44</v>
       </c>
       <c r="L12" s="4" t="n">
         <v>10841.58</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>10813.42</v>
+        <v>7913.86</v>
       </c>
     </row>
     <row r="13">
@@ -1283,16 +1283,16 @@
         <v>23364.5</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>10278.04</v>
+        <v>5773.37</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>33642.54</v>
+        <v>29137.87</v>
       </c>
       <c r="L13" s="4" t="n">
         <v>25373.65</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>8268.889999999999</v>
+        <v>3764.22</v>
       </c>
     </row>
     <row r="14">
@@ -1334,16 +1334,16 @@
         <v>12871.75</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>5662.28</v>
+        <v>3180.61</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>18534.03</v>
+        <v>16052.36</v>
       </c>
       <c r="L14" s="4" t="n">
         <v>18993.52</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-459.49</v>
+        <v>-2941.16</v>
       </c>
     </row>
     <row r="15">
@@ -1385,16 +1385,16 @@
         <v>34975.69</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>15385.81</v>
+        <v>8642.49</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>50361.5</v>
+        <v>43618.18</v>
       </c>
       <c r="L15" s="4" t="n">
         <v>66893.52</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-16532.02</v>
+        <v>-23275.34</v>
       </c>
     </row>
     <row r="16">
@@ -1436,16 +1436,16 @@
         <v>44172.32</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>19431.4</v>
+        <v>10914.98</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>63603.72</v>
+        <v>55087.3</v>
       </c>
       <c r="L16" s="4" t="n">
         <v>18993.52</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>44610.2</v>
+        <v>36093.78</v>
       </c>
     </row>
     <row r="17">
@@ -1487,16 +1487,16 @@
         <v>20516.88</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>9025.379999999999</v>
+        <v>5069.72</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>29542.26</v>
+        <v>25586.6</v>
       </c>
       <c r="L17" s="4" t="n">
         <v>18993.52</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>10548.74</v>
+        <v>6593.08</v>
       </c>
     </row>
     <row r="18">
@@ -1538,16 +1538,16 @@
         <v>12796.94</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>5629.37</v>
+        <v>3162.12</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>18426.31</v>
+        <v>15959.06</v>
       </c>
       <c r="L18" s="4" t="n">
         <v>18993.52</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-567.21</v>
+        <v>-3034.46</v>
       </c>
     </row>
     <row r="19">
@@ -1589,16 +1589,16 @@
         <v>19024.78</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>8369</v>
+        <v>4701.02</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>27393.78</v>
+        <v>23725.8</v>
       </c>
       <c r="L19" s="4" t="n">
         <v>18993.52</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>8400.26</v>
+        <v>4732.28</v>
       </c>
     </row>
     <row r="20">
@@ -1640,16 +1640,16 @@
         <v>39967.32</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>17581.63</v>
+        <v>9875.93</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>57548.95</v>
+        <v>49843.25</v>
       </c>
       <c r="L20" s="4" t="n">
         <v>63493.52</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-5944.57</v>
+        <v>-13650.27</v>
       </c>
     </row>
     <row r="21">
@@ -1691,16 +1691,16 @@
         <v>19926.53</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>8765.68</v>
+        <v>4923.85</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>28692.21</v>
+        <v>24850.38</v>
       </c>
       <c r="L21" s="4" t="n">
         <v>18993.52</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>9698.690000000001</v>
+        <v>5856.86</v>
       </c>
     </row>
     <row r="22">
@@ -1742,16 +1742,16 @@
         <v>19818.39</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>8718.110000000001</v>
+        <v>4897.12</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>28536.5</v>
+        <v>24715.51</v>
       </c>
       <c r="L22" s="4" t="n">
         <v>18993.52</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>9542.98</v>
+        <v>5721.99</v>
       </c>
     </row>
     <row r="23">
@@ -1793,16 +1793,16 @@
         <v>54126.01</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>23810.03</v>
+        <v>13374.54</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>77936.03999999999</v>
+        <v>67500.55</v>
       </c>
       <c r="L23" s="4" t="n">
         <v>66893.52</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>11042.52</v>
+        <v>607.03</v>
       </c>
     </row>
     <row r="24">
@@ -1844,16 +1844,16 @@
         <v>14545.69</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>6398.65</v>
+        <v>3594.24</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>20944.34</v>
+        <v>18139.93</v>
       </c>
       <c r="L24" s="4" t="n">
         <v>18993.52</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>1950.82</v>
+        <v>-853.59</v>
       </c>
     </row>
     <row r="25">
@@ -1895,16 +1895,16 @@
         <v>37770.76</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>16615.36</v>
+        <v>9333.16</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>54386.12</v>
+        <v>47103.92</v>
       </c>
       <c r="L25" s="4" t="n">
         <v>18993.52</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>35392.6</v>
+        <v>28110.4</v>
       </c>
     </row>
     <row r="26">
@@ -1946,16 +1946,16 @@
         <v>10599.91</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>4662.9</v>
+        <v>2619.24</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>15262.81</v>
+        <v>13219.15</v>
       </c>
       <c r="L26" s="4" t="n">
         <v>20835.13</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-5572.32</v>
+        <v>-7615.98</v>
       </c>
     </row>
     <row r="27">
@@ -1997,16 +1997,16 @@
         <v>8728.120000000001</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>3839.5</v>
+        <v>2156.72</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>12567.62</v>
+        <v>10884.84</v>
       </c>
       <c r="L27" s="4" t="n">
         <v>20835.13</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-8267.51</v>
+        <v>-9950.290000000001</v>
       </c>
     </row>
     <row r="28">
@@ -2048,16 +2048,16 @@
         <v>7873.66</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>3463.62</v>
+        <v>1945.58</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>11337.28</v>
+        <v>9819.24</v>
       </c>
       <c r="L28" s="4" t="n">
         <v>20835.13</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-9497.85</v>
+        <v>-11015.89</v>
       </c>
     </row>
     <row r="29">
@@ -2099,16 +2099,16 @@
         <v>6659.61</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>2929.56</v>
+        <v>1645.59</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>9589.17</v>
+        <v>8305.200000000001</v>
       </c>
       <c r="L29" s="4" t="n">
         <v>20835.13</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-11245.96</v>
+        <v>-12529.93</v>
       </c>
     </row>
     <row r="30">
@@ -2150,16 +2150,16 @@
         <v>7979.29</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>3510.09</v>
+        <v>1971.68</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>11489.38</v>
+        <v>9950.969999999999</v>
       </c>
       <c r="L30" s="4" t="n">
         <v>20835.13</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-9345.75</v>
+        <v>-10884.16</v>
       </c>
     </row>
     <row r="31">
@@ -2201,16 +2201,16 @@
         <v>7864.73</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>3459.7</v>
+        <v>1943.38</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>11324.43</v>
+        <v>9808.110000000001</v>
       </c>
       <c r="L31" s="4" t="n">
         <v>20835.13</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-9510.700000000001</v>
+        <v>-11027.02</v>
       </c>
     </row>
     <row r="32">
@@ -2252,16 +2252,16 @@
         <v>9268.290000000001</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>4077.12</v>
+        <v>2290.19</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>13345.41</v>
+        <v>11558.48</v>
       </c>
       <c r="L32" s="4" t="n">
         <v>20835.13</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-7489.72</v>
+        <v>-9276.65</v>
       </c>
     </row>
     <row r="33">
@@ -2303,16 +2303,16 @@
         <v>9535.82</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>4194.81</v>
+        <v>2356.3</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>13730.63</v>
+        <v>11892.12</v>
       </c>
       <c r="L33" s="4" t="n">
         <v>20835.13</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-7104.5</v>
+        <v>-8943.01</v>
       </c>
     </row>
     <row r="34">
@@ -2354,16 +2354,16 @@
         <v>10682.4</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>4699.19</v>
+        <v>2639.62</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>15381.59</v>
+        <v>13322.02</v>
       </c>
       <c r="L34" s="4" t="n">
         <v>20735.01</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-5353.42</v>
+        <v>-7412.99</v>
       </c>
     </row>
     <row r="35">
@@ -2405,16 +2405,16 @@
         <v>2868.83</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>1262</v>
+        <v>708.89</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>4130.83</v>
+        <v>3577.72</v>
       </c>
       <c r="L35" s="4" t="n">
         <v>1474</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>2656.83</v>
+        <v>2103.72</v>
       </c>
     </row>
     <row r="36">
@@ -2456,16 +2456,16 @@
         <v>3790.78</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>1667.56</v>
+        <v>936.7</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>5458.34</v>
+        <v>4727.48</v>
       </c>
       <c r="L36" s="4" t="n">
         <v>1374</v>
       </c>
       <c r="M36" s="4" t="n">
-        <v>4084.34</v>
+        <v>3353.48</v>
       </c>
     </row>
     <row r="37">
@@ -2507,16 +2507,373 @@
         <v>5936.69</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>2611.55</v>
+        <v>1466.96</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>8548.24</v>
+        <v>7403.65</v>
       </c>
       <c r="L37" s="4" t="n">
         <v>1374</v>
       </c>
       <c r="M37" s="4" t="n">
-        <v>7174.24</v>
+        <v>6029.65</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Digital Engineering</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>DIG-ENG</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>AM-ICAM-DIGENG</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>R-DIG-ENG-202501</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>6086.03</v>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>1332.84</v>
+      </c>
+      <c r="H38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="4" t="n">
+        <v>7418.87</v>
+      </c>
+      <c r="J38" s="4" t="n">
+        <v>1833.2</v>
+      </c>
+      <c r="K38" s="4" t="n">
+        <v>9252.07</v>
+      </c>
+      <c r="L38" s="4" t="n">
+        <v>82724.89</v>
+      </c>
+      <c r="M38" s="4" t="n">
+        <v>-73472.82000000001</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Digital Engineering</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>DIG-ENG</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>AM-ICAM-DIGENG</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>R-DIG-ENG-202502</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>4073.65</v>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>892.13</v>
+      </c>
+      <c r="H39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="4" t="n">
+        <v>4965.78</v>
+      </c>
+      <c r="J39" s="4" t="n">
+        <v>1227.04</v>
+      </c>
+      <c r="K39" s="4" t="n">
+        <v>6192.82</v>
+      </c>
+      <c r="L39" s="4" t="n">
+        <v>82724.89</v>
+      </c>
+      <c r="M39" s="4" t="n">
+        <v>-76532.07000000001</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Digital Engineering</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>DIG-ENG</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>AM-ICAM-DIGENG</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>R-DIG-ENG-202503</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>3603.17</v>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>789.1</v>
+      </c>
+      <c r="H40" s="4" t="n">
+        <v>100000</v>
+      </c>
+      <c r="I40" s="4" t="n">
+        <v>104392.27</v>
+      </c>
+      <c r="J40" s="4" t="n">
+        <v>25795.33</v>
+      </c>
+      <c r="K40" s="4" t="n">
+        <v>130187.6</v>
+      </c>
+      <c r="L40" s="4" t="n">
+        <v>82724.89</v>
+      </c>
+      <c r="M40" s="4" t="n">
+        <v>47462.71</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Digital Engineering</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>DIG-ENG</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>AM-ICAM-DIGENG</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>R-DIG-ENG-202504</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>6799.06</v>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>1488.99</v>
+      </c>
+      <c r="H41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="4" t="n">
+        <v>8288.049999999999</v>
+      </c>
+      <c r="J41" s="4" t="n">
+        <v>2047.98</v>
+      </c>
+      <c r="K41" s="4" t="n">
+        <v>10336.03</v>
+      </c>
+      <c r="L41" s="4" t="n">
+        <v>82724.89</v>
+      </c>
+      <c r="M41" s="4" t="n">
+        <v>-72388.86</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Digital Engineering</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>DIG-ENG</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>AM-ICAM-DIGENG</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>R-DIG-ENG-202505</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>4714.96</v>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>1032.58</v>
+      </c>
+      <c r="H42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="4" t="n">
+        <v>5747.54</v>
+      </c>
+      <c r="J42" s="4" t="n">
+        <v>1420.22</v>
+      </c>
+      <c r="K42" s="4" t="n">
+        <v>7167.76</v>
+      </c>
+      <c r="L42" s="4" t="n">
+        <v>82724.89</v>
+      </c>
+      <c r="M42" s="4" t="n">
+        <v>-75557.13</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Digital Engineering</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>DIG-ENG</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>AM-ICAM-DIGENG</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>R-DIG-ENG-202506</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>3452.3</v>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>756.05</v>
+      </c>
+      <c r="H43" s="4" t="n">
+        <v>69975.00999999999</v>
+      </c>
+      <c r="I43" s="4" t="n">
+        <v>74183.36</v>
+      </c>
+      <c r="J43" s="4" t="n">
+        <v>18330.71</v>
+      </c>
+      <c r="K43" s="4" t="n">
+        <v>92514.07000000001</v>
+      </c>
+      <c r="L43" s="4" t="n">
+        <v>82724.89</v>
+      </c>
+      <c r="M43" s="4" t="n">
+        <v>9789.18</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Digital Engineering</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>DIG-ENG</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>AM-ICAM-DIGENG</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>R-DIG-ENG-202507</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>1971.29</v>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>431.71</v>
+      </c>
+      <c r="H44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="4" t="n">
+        <v>2403</v>
+      </c>
+      <c r="J44" s="4" t="n">
+        <v>593.78</v>
+      </c>
+      <c r="K44" s="4" t="n">
+        <v>2996.78</v>
+      </c>
+      <c r="L44" s="4" t="n">
+        <v>82724.91</v>
+      </c>
+      <c r="M44" s="4" t="n">
+        <v>-79728.13</v>
       </c>
     </row>
   </sheetData>
@@ -2530,7 +2887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3997,6 +4354,279 @@
         <v>1374</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Digital Engineering</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="4" t="n">
+        <v>82724.89</v>
+      </c>
+      <c r="K38" s="4" t="n">
+        <v>82724.89</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Digital Engineering</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="4" t="n">
+        <v>82724.89</v>
+      </c>
+      <c r="K39" s="4" t="n">
+        <v>82724.89</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Digital Engineering</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="4" t="n">
+        <v>82724.89</v>
+      </c>
+      <c r="K40" s="4" t="n">
+        <v>82724.89</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Digital Engineering</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="4" t="n">
+        <v>82724.89</v>
+      </c>
+      <c r="K41" s="4" t="n">
+        <v>82724.89</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Digital Engineering</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="4" t="n">
+        <v>82724.89</v>
+      </c>
+      <c r="K42" s="4" t="n">
+        <v>82724.89</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Digital Engineering</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="4" t="n">
+        <v>82724.89</v>
+      </c>
+      <c r="K43" s="4" t="n">
+        <v>82724.89</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Digital Engineering</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="4" t="n">
+        <v>82724.91</v>
+      </c>
+      <c r="K44" s="4" t="n">
+        <v>82724.91</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/restated-2025/YBI-2025-AM-restated-invoices.xlsx
+++ b/docs/restated-2025/YBI-2025-AM-restated-invoices.xlsx
@@ -457,7 +457,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Fringe 21.90% · indirect combined 24.71% on MTDC · administrative labour POOL. Read from the rate on the record, not recomputed here.</t>
+          <t>Fringe 21.90% · indirect combined 22.48% on MTDC · administrative labour POOL. Read from the rate on the record, not recomputed here.</t>
         </is>
       </c>
     </row>
@@ -722,16 +722,16 @@
         <v>17486.88</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>4321.01</v>
+        <v>3931.05</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>21807.89</v>
+        <v>21417.93</v>
       </c>
       <c r="L2" s="4" t="n">
         <v>25373.65</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>-3565.76</v>
+        <v>-3955.72</v>
       </c>
     </row>
     <row r="3">
@@ -773,16 +773,16 @@
         <v>28659.7</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>7081.81</v>
+        <v>6442.7</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>35741.51</v>
+        <v>35102.4</v>
       </c>
       <c r="L3" s="4" t="n">
         <v>27798.15</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>7943.36</v>
+        <v>7304.25</v>
       </c>
     </row>
     <row r="4">
@@ -824,16 +824,16 @@
         <v>16621.06</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>4107.06</v>
+        <v>3736.41</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>20728.12</v>
+        <v>20357.47</v>
       </c>
       <c r="L4" s="4" t="n">
         <v>26032.42</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>-5304.3</v>
+        <v>-5674.95</v>
       </c>
     </row>
     <row r="5">
@@ -875,16 +875,16 @@
         <v>19336.76</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>4778.11</v>
+        <v>4346.9</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>24114.87</v>
+        <v>23683.66</v>
       </c>
       <c r="L5" s="4" t="n">
         <v>33785.53</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>-9670.66</v>
+        <v>-10101.87</v>
       </c>
     </row>
     <row r="6">
@@ -926,16 +926,16 @@
         <v>27752.41</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>6857.62</v>
+        <v>6238.74</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>34610.03</v>
+        <v>33991.15</v>
       </c>
       <c r="L6" s="4" t="n">
         <v>150719.52</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-116109.49</v>
+        <v>-116728.37</v>
       </c>
     </row>
     <row r="7">
@@ -977,16 +977,16 @@
         <v>17056.61</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>4214.69</v>
+        <v>3834.33</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>21271.3</v>
+        <v>20890.94</v>
       </c>
       <c r="L7" s="4" t="n">
         <v>29086.96</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-7815.66</v>
+        <v>-8196.02</v>
       </c>
     </row>
     <row r="8">
@@ -1028,16 +1028,16 @@
         <v>16783.79</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>4147.28</v>
+        <v>3773</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>20931.07</v>
+        <v>20556.79</v>
       </c>
       <c r="L8" s="4" t="n">
         <v>29073.65</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-8142.58</v>
+        <v>-8516.860000000001</v>
       </c>
     </row>
     <row r="9">
@@ -1079,16 +1079,16 @@
         <v>13664.93</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>3376.6</v>
+        <v>3071.88</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>17041.53</v>
+        <v>16736.81</v>
       </c>
       <c r="L9" s="4" t="n">
         <v>25940.16</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-8898.629999999999</v>
+        <v>-9203.35</v>
       </c>
     </row>
     <row r="10">
@@ -1130,16 +1130,16 @@
         <v>39984.38</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>9880.139999999999</v>
+        <v>8988.49</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>49864.52</v>
+        <v>48972.87</v>
       </c>
       <c r="L10" s="4" t="n">
         <v>132599.96</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-82735.44</v>
+        <v>-83627.09</v>
       </c>
     </row>
     <row r="11">
@@ -1181,16 +1181,16 @@
         <v>125701.62</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>31060.87</v>
+        <v>28257.72</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>156762.49</v>
+        <v>153959.34</v>
       </c>
       <c r="L11" s="4" t="n">
         <v>62615.64</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>94146.85000000001</v>
+        <v>91343.7</v>
       </c>
     </row>
     <row r="12">
@@ -1232,16 +1232,16 @@
         <v>15039.24</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>3716.2</v>
+        <v>3380.82</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>18755.44</v>
+        <v>18420.06</v>
       </c>
       <c r="L12" s="4" t="n">
         <v>10841.58</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>7913.86</v>
+        <v>7578.48</v>
       </c>
     </row>
     <row r="13">
@@ -1283,16 +1283,16 @@
         <v>23364.5</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>5773.37</v>
+        <v>5252.34</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>29137.87</v>
+        <v>28616.84</v>
       </c>
       <c r="L13" s="4" t="n">
         <v>25373.65</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>3764.22</v>
+        <v>3243.19</v>
       </c>
     </row>
     <row r="14">
@@ -1334,16 +1334,16 @@
         <v>12871.75</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>3180.61</v>
+        <v>2893.57</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>16052.36</v>
+        <v>15765.32</v>
       </c>
       <c r="L14" s="4" t="n">
         <v>18993.52</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-2941.16</v>
+        <v>-3228.2</v>
       </c>
     </row>
     <row r="15">
@@ -1385,16 +1385,16 @@
         <v>34975.69</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>8642.49</v>
+        <v>7862.54</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>43618.18</v>
+        <v>42838.23</v>
       </c>
       <c r="L15" s="4" t="n">
         <v>66893.52</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-23275.34</v>
+        <v>-24055.29</v>
       </c>
     </row>
     <row r="16">
@@ -1436,16 +1436,16 @@
         <v>44172.32</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>10914.98</v>
+        <v>9929.940000000001</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>55087.3</v>
+        <v>54102.26</v>
       </c>
       <c r="L16" s="4" t="n">
         <v>18993.52</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>36093.78</v>
+        <v>35108.74</v>
       </c>
     </row>
     <row r="17">
@@ -1487,16 +1487,16 @@
         <v>20516.88</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>5069.72</v>
+        <v>4612.2</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>25586.6</v>
+        <v>25129.08</v>
       </c>
       <c r="L17" s="4" t="n">
         <v>18993.52</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>6593.08</v>
+        <v>6135.56</v>
       </c>
     </row>
     <row r="18">
@@ -1538,16 +1538,16 @@
         <v>12796.94</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>3162.12</v>
+        <v>2876.75</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>15959.06</v>
+        <v>15673.69</v>
       </c>
       <c r="L18" s="4" t="n">
         <v>18993.52</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-3034.46</v>
+        <v>-3319.83</v>
       </c>
     </row>
     <row r="19">
@@ -1589,16 +1589,16 @@
         <v>19024.78</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>4701.02</v>
+        <v>4276.77</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>23725.8</v>
+        <v>23301.55</v>
       </c>
       <c r="L19" s="4" t="n">
         <v>18993.52</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>4732.28</v>
+        <v>4308.03</v>
       </c>
     </row>
     <row r="20">
@@ -1640,16 +1640,16 @@
         <v>39967.32</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>9875.93</v>
+        <v>8984.65</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>49843.25</v>
+        <v>48951.97</v>
       </c>
       <c r="L20" s="4" t="n">
         <v>63493.52</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-13650.27</v>
+        <v>-14541.55</v>
       </c>
     </row>
     <row r="21">
@@ -1691,16 +1691,16 @@
         <v>19926.53</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>4923.85</v>
+        <v>4479.48</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>24850.38</v>
+        <v>24406.01</v>
       </c>
       <c r="L21" s="4" t="n">
         <v>18993.52</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>5856.86</v>
+        <v>5412.49</v>
       </c>
     </row>
     <row r="22">
@@ -1742,16 +1742,16 @@
         <v>19818.39</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>4897.12</v>
+        <v>4455.17</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>24715.51</v>
+        <v>24273.56</v>
       </c>
       <c r="L22" s="4" t="n">
         <v>18993.52</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>5721.99</v>
+        <v>5280.04</v>
       </c>
     </row>
     <row r="23">
@@ -1793,16 +1793,16 @@
         <v>54126.01</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>13374.54</v>
+        <v>12167.53</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>67500.55</v>
+        <v>66293.53999999999</v>
       </c>
       <c r="L23" s="4" t="n">
         <v>66893.52</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>607.03</v>
+        <v>-599.98</v>
       </c>
     </row>
     <row r="24">
@@ -1844,16 +1844,16 @@
         <v>14545.69</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>3594.24</v>
+        <v>3269.87</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>18139.93</v>
+        <v>17815.56</v>
       </c>
       <c r="L24" s="4" t="n">
         <v>18993.52</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-853.59</v>
+        <v>-1177.96</v>
       </c>
     </row>
     <row r="25">
@@ -1895,16 +1895,16 @@
         <v>37770.76</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>9333.16</v>
+        <v>8490.870000000001</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>47103.92</v>
+        <v>46261.63</v>
       </c>
       <c r="L25" s="4" t="n">
         <v>18993.52</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>28110.4</v>
+        <v>27268.11</v>
       </c>
     </row>
     <row r="26">
@@ -1946,16 +1946,16 @@
         <v>10599.91</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>2619.24</v>
+        <v>2382.86</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>13219.15</v>
+        <v>12982.77</v>
       </c>
       <c r="L26" s="4" t="n">
         <v>20835.13</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-7615.98</v>
+        <v>-7852.36</v>
       </c>
     </row>
     <row r="27">
@@ -1997,16 +1997,16 @@
         <v>8728.120000000001</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>2156.72</v>
+        <v>1962.08</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>10884.84</v>
+        <v>10690.2</v>
       </c>
       <c r="L27" s="4" t="n">
         <v>20835.13</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-9950.290000000001</v>
+        <v>-10144.93</v>
       </c>
     </row>
     <row r="28">
@@ -2048,16 +2048,16 @@
         <v>7873.66</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>1945.58</v>
+        <v>1770</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>9819.24</v>
+        <v>9643.66</v>
       </c>
       <c r="L28" s="4" t="n">
         <v>20835.13</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-11015.89</v>
+        <v>-11191.47</v>
       </c>
     </row>
     <row r="29">
@@ -2099,16 +2099,16 @@
         <v>6659.61</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>1645.59</v>
+        <v>1497.08</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>8305.200000000001</v>
+        <v>8156.69</v>
       </c>
       <c r="L29" s="4" t="n">
         <v>20835.13</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-12529.93</v>
+        <v>-12678.44</v>
       </c>
     </row>
     <row r="30">
@@ -2150,16 +2150,16 @@
         <v>7979.29</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>1971.68</v>
+        <v>1793.75</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>9950.969999999999</v>
+        <v>9773.040000000001</v>
       </c>
       <c r="L30" s="4" t="n">
         <v>20835.13</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-10884.16</v>
+        <v>-11062.09</v>
       </c>
     </row>
     <row r="31">
@@ -2201,16 +2201,16 @@
         <v>7864.73</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>1943.38</v>
+        <v>1767.99</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>9808.110000000001</v>
+        <v>9632.719999999999</v>
       </c>
       <c r="L31" s="4" t="n">
         <v>20835.13</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-11027.02</v>
+        <v>-11202.41</v>
       </c>
     </row>
     <row r="32">
@@ -2252,16 +2252,16 @@
         <v>9268.290000000001</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>2290.19</v>
+        <v>2083.51</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>11558.48</v>
+        <v>11351.8</v>
       </c>
       <c r="L32" s="4" t="n">
         <v>20835.13</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-9276.65</v>
+        <v>-9483.33</v>
       </c>
     </row>
     <row r="33">
@@ -2303,16 +2303,16 @@
         <v>9535.82</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>2356.3</v>
+        <v>2143.65</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>11892.12</v>
+        <v>11679.47</v>
       </c>
       <c r="L33" s="4" t="n">
         <v>20835.13</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-8943.01</v>
+        <v>-9155.66</v>
       </c>
     </row>
     <row r="34">
@@ -2354,16 +2354,16 @@
         <v>10682.4</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>2639.62</v>
+        <v>2401.4</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>13322.02</v>
+        <v>13083.8</v>
       </c>
       <c r="L34" s="4" t="n">
         <v>20735.01</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-7412.99</v>
+        <v>-7651.21</v>
       </c>
     </row>
     <row r="35">
@@ -2405,16 +2405,16 @@
         <v>2868.83</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>708.89</v>
+        <v>644.91</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>3577.72</v>
+        <v>3513.74</v>
       </c>
       <c r="L35" s="4" t="n">
         <v>1474</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>2103.72</v>
+        <v>2039.74</v>
       </c>
     </row>
     <row r="36">
@@ -2456,16 +2456,16 @@
         <v>3790.78</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>936.7</v>
+        <v>852.17</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>4727.48</v>
+        <v>4642.95</v>
       </c>
       <c r="L36" s="4" t="n">
         <v>1374</v>
       </c>
       <c r="M36" s="4" t="n">
-        <v>3353.48</v>
+        <v>3268.95</v>
       </c>
     </row>
     <row r="37">
@@ -2507,16 +2507,16 @@
         <v>5936.69</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>1466.96</v>
+        <v>1334.57</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>7403.65</v>
+        <v>7271.26</v>
       </c>
       <c r="L37" s="4" t="n">
         <v>1374</v>
       </c>
       <c r="M37" s="4" t="n">
-        <v>6029.65</v>
+        <v>5897.26</v>
       </c>
     </row>
     <row r="38">
@@ -2558,16 +2558,16 @@
         <v>7418.87</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>1833.2</v>
+        <v>1667.76</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>9252.07</v>
+        <v>9086.629999999999</v>
       </c>
       <c r="L38" s="4" t="n">
         <v>82724.89</v>
       </c>
       <c r="M38" s="4" t="n">
-        <v>-73472.82000000001</v>
+        <v>-73638.25999999999</v>
       </c>
     </row>
     <row r="39">
@@ -2609,16 +2609,16 @@
         <v>4965.78</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>1227.04</v>
+        <v>1116.31</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>6192.82</v>
+        <v>6082.09</v>
       </c>
       <c r="L39" s="4" t="n">
         <v>82724.89</v>
       </c>
       <c r="M39" s="4" t="n">
-        <v>-76532.07000000001</v>
+        <v>-76642.8</v>
       </c>
     </row>
     <row r="40">
@@ -2660,16 +2660,16 @@
         <v>104392.27</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>25795.33</v>
+        <v>23467.38</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>130187.6</v>
+        <v>127859.65</v>
       </c>
       <c r="L40" s="4" t="n">
         <v>82724.89</v>
       </c>
       <c r="M40" s="4" t="n">
-        <v>47462.71</v>
+        <v>45134.76</v>
       </c>
     </row>
     <row r="41">
@@ -2711,16 +2711,16 @@
         <v>8288.049999999999</v>
       </c>
       <c r="J41" s="4" t="n">
-        <v>2047.98</v>
+        <v>1863.15</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>10336.03</v>
+        <v>10151.2</v>
       </c>
       <c r="L41" s="4" t="n">
         <v>82724.89</v>
       </c>
       <c r="M41" s="4" t="n">
-        <v>-72388.86</v>
+        <v>-72573.69</v>
       </c>
     </row>
     <row r="42">
@@ -2762,16 +2762,16 @@
         <v>5747.54</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>1420.22</v>
+        <v>1292.05</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>7167.76</v>
+        <v>7039.59</v>
       </c>
       <c r="L42" s="4" t="n">
         <v>82724.89</v>
       </c>
       <c r="M42" s="4" t="n">
-        <v>-75557.13</v>
+        <v>-75685.3</v>
       </c>
     </row>
     <row r="43">
@@ -2813,16 +2813,16 @@
         <v>74183.36</v>
       </c>
       <c r="J43" s="4" t="n">
-        <v>18330.71</v>
+        <v>16676.42</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>92514.07000000001</v>
+        <v>90859.78</v>
       </c>
       <c r="L43" s="4" t="n">
         <v>82724.89</v>
       </c>
       <c r="M43" s="4" t="n">
-        <v>9789.18</v>
+        <v>8134.89</v>
       </c>
     </row>
     <row r="44">
@@ -2864,16 +2864,16 @@
         <v>2403</v>
       </c>
       <c r="J44" s="4" t="n">
-        <v>593.78</v>
+        <v>540.2</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>2996.78</v>
+        <v>2943.2</v>
       </c>
       <c r="L44" s="4" t="n">
         <v>82724.91</v>
       </c>
       <c r="M44" s="4" t="n">
-        <v>-79728.13</v>
+        <v>-79781.71000000001</v>
       </c>
     </row>
   </sheetData>
